--- a/financial-projections/Blockmediary_Financial_Model_FullRisk.xlsx
+++ b/financial-projections/Blockmediary_Financial_Model_FullRisk.xlsx
@@ -6875,7 +6875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B66"/>
+  <dimension ref="B2:B72"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7145,6 +7145,41 @@
     <row r="66" spans="2:2">
       <c r="B66" s="57" t="s">
         <v>1199</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSUMPTIONS FLAGGED IN REVIEW (address later) - added 2026-07-01:</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Growth: base case stacks ~250%/yr deal-count growth (180 -&gt; 30,000 by Yr5) AND +35%/yr avg deal value (25k -&gt; 83k GBP), compounding into 2.49bn GBP GMV. Each is aggressive alone; multiplied they are the number investors will push hardest on. The 35% deal-value growth has no stated basis - revisit / justify or dampen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Deal size vs MVP cap: avg deal value passes the 50k GBP auto-processing cap (domain-rules.md) in Yr4 (61.5k) and Yr5 (83k), so most later-year deals fall outside the automated tier into mandatory human review - a cost the fixed headcount does not obviously absorb. Raise the cap or cost the extra review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Fixed-cost scaling: headcount grows 9 -&gt; ~21 FTE while volume grows 166x. Per-deal ops is in COGS, but 6 compliance/ops FTE overseeing 2.5bn GBP of regulated escrow + ~1,890 disputes + ~3,600 QA reviews looks thin, and it is what produces the 73% Yr5 EBITDA margin. Pressure-test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. New-counterparty share: fixed at 50% every year -&gt; 30,000 new counterparties onboarded in Yr5 vs only 3,000 active customers, inconsistent with rising repeat usage (deals/customer -&gt; 10). Share should decline as the base matures; currently inflates both KYC/KYB cost and onboarding-fee revenue.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7510,28 +7545,22 @@
         <v>1154</v>
       </c>
       <c r="B5" s="71">
-        <f>IF(1=1,IFERROR(ROUND(-MIN('P&amp;L_5yr'!C7,'P&amp;L_5yr'!C70)*('P&amp;L_5yr'!C14/'P&amp;L_5yr'!C7)*Assumptions!$F$115,0),0),0)</f>
-        <v>-10106</v>
+        <f>IFERROR(ROUND(-'P&amp;L_5yr'!C70*('P&amp;L_5yr'!C14/'P&amp;L_5yr'!C7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="C5" s="71">
-        <f>IF(2=1,IFERROR(ROUND(-MIN('P&amp;L_5yr'!D7,'P&amp;L_5yr'!D70)*('P&amp;L_5yr'!D14/'P&amp;L_5yr'!D7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,'P&amp;L_5yr'!D70-'P&amp;L_5yr'!C70)*('P&amp;L_5yr'!D14/'P&amp;L_5yr'!D7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="D5" s="71">
-        <f>IF(3=1,IFERROR(ROUND(-MIN('P&amp;L_5yr'!E7,'P&amp;L_5yr'!E70)*('P&amp;L_5yr'!E14/'P&amp;L_5yr'!E7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,'P&amp;L_5yr'!E70-'P&amp;L_5yr'!D70)*('P&amp;L_5yr'!E14/'P&amp;L_5yr'!E7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="E5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN('P&amp;L_5yr'!F7,'P&amp;L_5yr'!F70)*('P&amp;L_5yr'!F14/'P&amp;L_5yr'!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,'P&amp;L_5yr'!F70-'P&amp;L_5yr'!E70)*('P&amp;L_5yr'!F14/'P&amp;L_5yr'!F7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="F5" s="89">
-        <f>IF(5=1,IFERROR(ROUND(-MIN('P&amp;L_5yr'!G7,'P&amp;L_5yr'!G70)*('P&amp;L_5yr'!G14/'P&amp;L_5yr'!G7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,'P&amp;L_5yr'!G70-'P&amp;L_5yr'!F70)*('P&amp;L_5yr'!G14/'P&amp;L_5yr'!G7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="G5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN('P&amp;L_5yr'!F7,'P&amp;L_5yr'!F70)*('P&amp;L_5yr'!F14/'P&amp;L_5yr'!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,'P&amp;L_5yr'!F70-'P&amp;L_5yr'!E70)*('P&amp;L_5yr'!F14/'P&amp;L_5yr'!F7)*Assumptions!$F$115,0),0)</f>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1">
@@ -7875,28 +7904,22 @@
         <v>435</v>
       </c>
       <c r="B19" s="71">
-        <f>ROUND('P&amp;L_5yr'!C7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>8100</v>
+        <f>ROUND('P&amp;L_5yr'!C12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="C19" s="71">
-        <f>ROUND('P&amp;L_5yr'!D7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>67500</v>
+        <f>ROUND('P&amp;L_5yr'!D12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="D19" s="71">
-        <f>ROUND('P&amp;L_5yr'!E7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>270000</v>
+        <f>ROUND('P&amp;L_5yr'!E12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="E19" s="89">
-        <f>ROUND('P&amp;L_5yr'!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>675000</v>
+        <f>ROUND('P&amp;L_5yr'!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="F19" s="89">
-        <f>ROUND('P&amp;L_5yr'!G7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>1350000</v>
+        <f>ROUND('P&amp;L_5yr'!G12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="G19" s="89">
-        <f>ROUND('P&amp;L_5yr'!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>675000</v>
+        <f>ROUND('P&amp;L_5yr'!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1">
@@ -7933,28 +7956,22 @@
         <v>446</v>
       </c>
       <c r="B21" s="71">
-        <f>ROUND('P&amp;L_5yr'!C18*Assumptions!$F$144,0)</f>
-        <v>5339</v>
+        <v>0</v>
       </c>
       <c r="C21" s="71">
-        <f>ROUND('P&amp;L_5yr'!D18*Assumptions!$F$144,0)</f>
-        <v>47615</v>
+        <f>ROUND('P&amp;L_5yr'!D18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="D21" s="71">
-        <f>ROUND('P&amp;L_5yr'!E18*Assumptions!$F$144,0)</f>
-        <v>185344</v>
+        <f>ROUND('P&amp;L_5yr'!E18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="E21" s="89">
-        <f>ROUND('P&amp;L_5yr'!F18*Assumptions!$F$144,0)</f>
-        <v>486276</v>
+        <f>ROUND('P&amp;L_5yr'!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="F21" s="89">
-        <f>ROUND('P&amp;L_5yr'!G18*Assumptions!$F$144,0)</f>
-        <v>1135011</v>
+        <f>ROUND('P&amp;L_5yr'!G18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="G21" s="89">
-        <f>ROUND('P&amp;L_5yr'!F18*Assumptions!$F$144,0)</f>
-        <v>486276</v>
+        <f>ROUND('P&amp;L_5yr'!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1">
@@ -10990,28 +11007,22 @@
         <v>1154</v>
       </c>
       <c r="B5" s="71">
-        <f>IF(1=1,IFERROR(ROUND(-MIN(Scenario_Low_PL!C7,Scenario_Low_PL!C70)*(Scenario_Low_PL!C14/Scenario_Low_PL!C7)*Assumptions!$F$115,0),0),0)</f>
-        <v>-8413</v>
+        <f>IFERROR(ROUND(-Scenario_Low_PL!C70*(Scenario_Low_PL!C14/Scenario_Low_PL!C7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="C5" s="71">
-        <f>IF(2=1,IFERROR(ROUND(-MIN(Scenario_Low_PL!D7,Scenario_Low_PL!D70)*(Scenario_Low_PL!D14/Scenario_Low_PL!D7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Low_PL!D70-Scenario_Low_PL!C70)*(Scenario_Low_PL!D14/Scenario_Low_PL!D7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="D5" s="71">
-        <f>IF(3=1,IFERROR(ROUND(-MIN(Scenario_Low_PL!E7,Scenario_Low_PL!E70)*(Scenario_Low_PL!E14/Scenario_Low_PL!E7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Low_PL!E70-Scenario_Low_PL!D70)*(Scenario_Low_PL!E14/Scenario_Low_PL!E7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="E5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN(Scenario_Low_PL!F7,Scenario_Low_PL!F70)*(Scenario_Low_PL!F14/Scenario_Low_PL!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Low_PL!F70-Scenario_Low_PL!E70)*(Scenario_Low_PL!F14/Scenario_Low_PL!F7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="F5" s="89">
-        <f>IF(5=1,IFERROR(ROUND(-MIN(Scenario_Low_PL!G7,Scenario_Low_PL!G70)*(Scenario_Low_PL!G14/Scenario_Low_PL!G7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Low_PL!G70-Scenario_Low_PL!F70)*(Scenario_Low_PL!G14/Scenario_Low_PL!G7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="G5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN(Scenario_Low_PL!F7,Scenario_Low_PL!F70)*(Scenario_Low_PL!F14/Scenario_Low_PL!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Low_PL!F70-Scenario_Low_PL!E70)*(Scenario_Low_PL!F14/Scenario_Low_PL!F7)*Assumptions!$F$115,0),0)</f>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1">
@@ -11355,28 +11366,22 @@
         <v>435</v>
       </c>
       <c r="B19" s="71">
-        <f>ROUND(Scenario_Low_PL!C7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>2700</v>
+        <f>ROUND(Scenario_Low_PL!C12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="C19" s="71">
-        <f>ROUND(Scenario_Low_PL!D7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>13500</v>
+        <f>ROUND(Scenario_Low_PL!D12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="D19" s="71">
-        <f>ROUND(Scenario_Low_PL!E7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>40500</v>
+        <f>ROUND(Scenario_Low_PL!E12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="E19" s="89">
-        <f>ROUND(Scenario_Low_PL!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>81000</v>
+        <f>ROUND(Scenario_Low_PL!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="F19" s="89">
-        <f>ROUND(Scenario_Low_PL!G7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>270000</v>
+        <f>ROUND(Scenario_Low_PL!G12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="G19" s="89">
-        <f>ROUND(Scenario_Low_PL!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>81000</v>
+        <f>ROUND(Scenario_Low_PL!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1">
@@ -11413,28 +11418,22 @@
         <v>446</v>
       </c>
       <c r="B21" s="71">
-        <f>ROUND(Scenario_Low_PL!C18*Assumptions!$F$144,0)</f>
-        <v>2210</v>
+        <v>0</v>
       </c>
       <c r="C21" s="71">
-        <f>ROUND(Scenario_Low_PL!D18*Assumptions!$F$144,0)</f>
-        <v>13258</v>
+        <f>ROUND(Scenario_Low_PL!D18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="D21" s="71">
-        <f>ROUND(Scenario_Low_PL!E18*Assumptions!$F$144,0)</f>
-        <v>40286</v>
+        <f>ROUND(Scenario_Low_PL!E18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="E21" s="89">
-        <f>ROUND(Scenario_Low_PL!F18*Assumptions!$F$144,0)</f>
-        <v>82475</v>
+        <f>ROUND(Scenario_Low_PL!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="F21" s="89">
-        <f>ROUND(Scenario_Low_PL!G18*Assumptions!$F$144,0)</f>
-        <v>295312</v>
+        <f>ROUND(Scenario_Low_PL!G18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="G21" s="89">
-        <f>ROUND(Scenario_Low_PL!F18*Assumptions!$F$144,0)</f>
-        <v>82475</v>
+        <f>ROUND(Scenario_Low_PL!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1">
@@ -16323,28 +16322,22 @@
         <v>1154</v>
       </c>
       <c r="B5" s="71">
-        <f>IF(1=1,IFERROR(ROUND(-MIN(Scenario_Base_PL!C7,Scenario_Base_PL!C70)*(Scenario_Base_PL!C14/Scenario_Base_PL!C7)*Assumptions!$F$115,0),0),0)</f>
-        <v>-10106</v>
+        <f>IFERROR(ROUND(-Scenario_Base_PL!C70*(Scenario_Base_PL!C14/Scenario_Base_PL!C7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="C5" s="71">
-        <f>IF(2=1,IFERROR(ROUND(-MIN(Scenario_Base_PL!D7,Scenario_Base_PL!D70)*(Scenario_Base_PL!D14/Scenario_Base_PL!D7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Base_PL!D70-Scenario_Base_PL!C70)*(Scenario_Base_PL!D14/Scenario_Base_PL!D7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="D5" s="71">
-        <f>IF(3=1,IFERROR(ROUND(-MIN(Scenario_Base_PL!E7,Scenario_Base_PL!E70)*(Scenario_Base_PL!E14/Scenario_Base_PL!E7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Base_PL!E70-Scenario_Base_PL!D70)*(Scenario_Base_PL!E14/Scenario_Base_PL!E7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="E5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN(Scenario_Base_PL!F7,Scenario_Base_PL!F70)*(Scenario_Base_PL!F14/Scenario_Base_PL!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Base_PL!F70-Scenario_Base_PL!E70)*(Scenario_Base_PL!F14/Scenario_Base_PL!F7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="F5" s="89">
-        <f>IF(5=1,IFERROR(ROUND(-MIN(Scenario_Base_PL!G7,Scenario_Base_PL!G70)*(Scenario_Base_PL!G14/Scenario_Base_PL!G7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Base_PL!G70-Scenario_Base_PL!F70)*(Scenario_Base_PL!G14/Scenario_Base_PL!G7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="G5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN(Scenario_Base_PL!F7,Scenario_Base_PL!F70)*(Scenario_Base_PL!F14/Scenario_Base_PL!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_Base_PL!F70-Scenario_Base_PL!E70)*(Scenario_Base_PL!F14/Scenario_Base_PL!F7)*Assumptions!$F$115,0),0)</f>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1">
@@ -16688,28 +16681,22 @@
         <v>435</v>
       </c>
       <c r="B19" s="71">
-        <f>ROUND(Scenario_Base_PL!C7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>8100</v>
+        <f>ROUND(Scenario_Base_PL!C12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="C19" s="71">
-        <f>ROUND(Scenario_Base_PL!D7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>67500</v>
+        <f>ROUND(Scenario_Base_PL!D12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="D19" s="71">
-        <f>ROUND(Scenario_Base_PL!E7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>270000</v>
+        <f>ROUND(Scenario_Base_PL!E12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="E19" s="89">
-        <f>ROUND(Scenario_Base_PL!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>675000</v>
+        <f>ROUND(Scenario_Base_PL!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="F19" s="89">
-        <f>ROUND(Scenario_Base_PL!G7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>1350000</v>
+        <f>ROUND(Scenario_Base_PL!G12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="G19" s="89">
-        <f>ROUND(Scenario_Base_PL!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>675000</v>
+        <f>ROUND(Scenario_Base_PL!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1">
@@ -16746,28 +16733,22 @@
         <v>446</v>
       </c>
       <c r="B21" s="71">
-        <f>ROUND(Scenario_Base_PL!C18*Assumptions!$F$144,0)</f>
-        <v>5339</v>
+        <v>0</v>
       </c>
       <c r="C21" s="71">
-        <f>ROUND(Scenario_Base_PL!D18*Assumptions!$F$144,0)</f>
-        <v>47615</v>
+        <f>ROUND(Scenario_Base_PL!D18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="D21" s="71">
-        <f>ROUND(Scenario_Base_PL!E18*Assumptions!$F$144,0)</f>
-        <v>185344</v>
+        <f>ROUND(Scenario_Base_PL!E18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="E21" s="89">
-        <f>ROUND(Scenario_Base_PL!F18*Assumptions!$F$144,0)</f>
-        <v>486276</v>
+        <f>ROUND(Scenario_Base_PL!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="F21" s="89">
-        <f>ROUND(Scenario_Base_PL!G18*Assumptions!$F$144,0)</f>
-        <v>1135011</v>
+        <f>ROUND(Scenario_Base_PL!G18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="G21" s="89">
-        <f>ROUND(Scenario_Base_PL!F18*Assumptions!$F$144,0)</f>
-        <v>486276</v>
+        <f>ROUND(Scenario_Base_PL!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1">
@@ -21656,28 +21637,22 @@
         <v>1154</v>
       </c>
       <c r="B5" s="71">
-        <f>IF(1=1,IFERROR(ROUND(-MIN(Scenario_High_PL!C7,Scenario_High_PL!C70)*(Scenario_High_PL!C14/Scenario_High_PL!C7)*Assumptions!$F$115,0),0),0)</f>
-        <v>-6844</v>
+        <f>IFERROR(ROUND(-Scenario_High_PL!C70*(Scenario_High_PL!C14/Scenario_High_PL!C7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="C5" s="71">
-        <f>IF(2=1,IFERROR(ROUND(-MIN(Scenario_High_PL!D7,Scenario_High_PL!D70)*(Scenario_High_PL!D14/Scenario_High_PL!D7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_High_PL!D70-Scenario_High_PL!C70)*(Scenario_High_PL!D14/Scenario_High_PL!D7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="D5" s="71">
-        <f>IF(3=1,IFERROR(ROUND(-MIN(Scenario_High_PL!E7,Scenario_High_PL!E70)*(Scenario_High_PL!E14/Scenario_High_PL!E7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_High_PL!E70-Scenario_High_PL!D70)*(Scenario_High_PL!E14/Scenario_High_PL!E7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="E5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN(Scenario_High_PL!F7,Scenario_High_PL!F70)*(Scenario_High_PL!F14/Scenario_High_PL!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_High_PL!F70-Scenario_High_PL!E70)*(Scenario_High_PL!F14/Scenario_High_PL!F7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="F5" s="89">
-        <f>IF(5=1,IFERROR(ROUND(-MIN(Scenario_High_PL!G7,Scenario_High_PL!G70)*(Scenario_High_PL!G14/Scenario_High_PL!G7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_High_PL!G70-Scenario_High_PL!F70)*(Scenario_High_PL!G14/Scenario_High_PL!G7)*Assumptions!$F$115,0),0)</f>
       </c>
       <c r="G5" s="89">
-        <f>IF(4=1,IFERROR(ROUND(-MIN(Scenario_High_PL!F7,Scenario_High_PL!F70)*(Scenario_High_PL!F14/Scenario_High_PL!F7)*Assumptions!$F$115,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(-MAX(0,Scenario_High_PL!F70-Scenario_High_PL!E70)*(Scenario_High_PL!F14/Scenario_High_PL!F7)*Assumptions!$F$115,0),0)</f>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1">
@@ -22021,28 +21996,22 @@
         <v>435</v>
       </c>
       <c r="B19" s="71">
-        <f>ROUND(Scenario_High_PL!C7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>11250</v>
+        <f>ROUND(Scenario_High_PL!C12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="C19" s="71">
-        <f>ROUND(Scenario_High_PL!D7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>144000</v>
+        <f>ROUND(Scenario_High_PL!D12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="D19" s="71">
-        <f>ROUND(Scenario_High_PL!E7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>675000</v>
+        <f>ROUND(Scenario_High_PL!E12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="E19" s="89">
-        <f>ROUND(Scenario_High_PL!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>1440000</v>
+        <f>ROUND(Scenario_High_PL!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="F19" s="89">
-        <f>ROUND(Scenario_High_PL!G7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>3150000</v>
+        <f>ROUND(Scenario_High_PL!G12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
       <c r="G19" s="89">
-        <f>ROUND(Scenario_High_PL!F7*Assumptions!$F$138*Assumptions!$F$139,0)</f>
-        <v>1440000</v>
+        <f>ROUND(Scenario_High_PL!F12*Assumptions!$F$138*Assumptions!$F$139,0)</f>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1">
@@ -22079,28 +22048,22 @@
         <v>446</v>
       </c>
       <c r="B21" s="71">
-        <f>ROUND(Scenario_High_PL!C18*Assumptions!$F$144,0)</f>
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="C21" s="71">
-        <f>ROUND(Scenario_High_PL!D18*Assumptions!$F$144,0)</f>
-        <v>80520</v>
+        <f>ROUND(Scenario_High_PL!D18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="D21" s="71">
-        <f>ROUND(Scenario_High_PL!E18*Assumptions!$F$144,0)</f>
-        <v>363482</v>
+        <f>ROUND(Scenario_High_PL!E18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="E21" s="89">
-        <f>ROUND(Scenario_High_PL!F18*Assumptions!$F$144,0)</f>
-        <v>877385</v>
+        <f>ROUND(Scenario_High_PL!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="F21" s="89">
-        <f>ROUND(Scenario_High_PL!G18*Assumptions!$F$144,0)</f>
-        <v>2339493</v>
+        <f>ROUND(Scenario_High_PL!G18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
       <c r="G21" s="89">
-        <f>ROUND(Scenario_High_PL!F18*Assumptions!$F$144,0)</f>
-        <v>877385</v>
+        <f>ROUND(Scenario_High_PL!F18*Assumptions!$F$167*Assumptions!$F$144,0)</f>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1">
@@ -28862,7 +28825,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -30100,8 +30063,10 @@
       <c r="G73" s="163" t="s">
         <v>295</v>
       </c>
-      <c r="H73" s="68" t="s">
-        <v>296</v>
+      <c r="H73" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed input; not scenario-driven. Tier A eBL/source-of-truth rail: 0.65% GMV. Placeholder pending competitor benchmarking; hold high unless competition requires lowering.</t>
+        </is>
       </c>
     </row>
     <row r="74" spans="2:8" ht="13.5" customHeight="1">
@@ -30117,8 +30082,10 @@
       <c r="G74" s="163" t="s">
         <v>295</v>
       </c>
-      <c r="H74" s="68" t="s">
-        <v>298</v>
+      <c r="H74" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed input; not scenario-driven. Tier B carrier/API-verified docs: 0.90% GMV. Placeholder pending competitor benchmarking; hold high unless competition requires lowering.</t>
+        </is>
       </c>
     </row>
     <row r="75" spans="2:8" ht="13.5" customHeight="1">
@@ -30134,8 +30101,10 @@
       <c r="G75" s="163" t="s">
         <v>295</v>
       </c>
-      <c r="H75" s="68" t="s">
-        <v>300</v>
+      <c r="H75" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed input; not scenario-driven. Tier C paper/originals fallback: 2.0% GMV. High-risk manual fallback; placeholder pending competitor benchmarking, hold high unless competition requires lowering.</t>
+        </is>
       </c>
     </row>
     <row r="76" spans="2:8" ht="13.5" customHeight="1">
@@ -31210,13 +31179,17 @@
       <c r="D138" s="161"/>
       <c r="E138" s="161"/>
       <c r="F138" s="162">
-        <v>0.03</v>
-      </c>
-      <c r="G138" s="163" t="s">
-        <v>276</v>
-      </c>
-      <c r="H138" s="68" t="s">
-        <v>434</v>
+        <v>0.15</v>
+      </c>
+      <c r="G138" s="163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% disputed deals</t>
+        </is>
+      </c>
+      <c r="H138" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed input; not scenario-driven. Share of DISPUTED deals escalating to formal external forum / expert determination (previously modelled as 3% of ALL deals stacked on tier dispute rates). Estimate - refine.</t>
+        </is>
       </c>
     </row>
     <row r="139" spans="2:8" ht="13.5" customHeight="1">
@@ -31317,8 +31290,10 @@
       <c r="G144" s="163" t="s">
         <v>438</v>
       </c>
-      <c r="H144" s="68" t="s">
-        <v>447</v>
+      <c r="H144" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed input; not scenario-driven. Forwarder/platform referral/revenue share; applied to partner-sourced revenue only (F167), not total revenue.</t>
+        </is>
       </c>
     </row>
     <row r="145" spans="2:8" ht="13.5" customHeight="1">
@@ -31771,6 +31746,26 @@
       </c>
       <c r="H166" s="183" t="s">
         <v>490</v>
+      </c>
+    </row>
+    <row r="167" spans="2:8">
+      <c r="B167" s="160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partner-sourced revenue share</t>
+        </is>
+      </c>
+      <c r="F167" s="162">
+        <v>0.3</v>
+      </c>
+      <c r="G167" s="163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% revenue</t>
+        </is>
+      </c>
+      <c r="H167" s="183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed input; not scenario-driven. Est. share of revenue via partner/channel deals; partner commission (F144) applies only to this share, not total revenue. Planning estimate - refine, ideally by year.</t>
+        </is>
       </c>
     </row>
   </sheetData>
